--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_00F124D0156748DFE54878D6425DCE3A874750C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BB0AAB4-F852-4B46-A3E4-659BDC8C2D56}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DDC35D9-D645-40B6-B7D9-E184D1DA433F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
   <si>
     <t>Año</t>
   </si>
@@ -66,6 +53,78 @@
   </si>
   <si>
     <t>Fecha cambio</t>
+  </si>
+  <si>
+    <t>Enero</t>
+  </si>
+  <si>
+    <t>Venta directa - salarial</t>
+  </si>
+  <si>
+    <t>Auxiliar</t>
+  </si>
+  <si>
+    <t>Natalia  Giraldo Galeano</t>
+  </si>
+  <si>
+    <t>110.0%</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>Raiza Lorena Urzola Lora</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>Yessica Yulieth Moreno</t>
+  </si>
+  <si>
+    <t>15.0%</t>
+  </si>
+  <si>
+    <t>Referido - bono</t>
+  </si>
+  <si>
+    <t>Líder</t>
+  </si>
+  <si>
+    <t>Maria Deisy Gil Gomez</t>
+  </si>
+  <si>
+    <t>44.2%</t>
+  </si>
+  <si>
+    <t>Pyme Móvil - salarial</t>
+  </si>
+  <si>
+    <t>Sin meta</t>
+  </si>
+  <si>
+    <t>CLOUND - salarial</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>157.5%</t>
+  </si>
+  <si>
+    <t>187.5%</t>
+  </si>
+  <si>
+    <t>117.5%</t>
+  </si>
+  <si>
+    <t>92.5%</t>
+  </si>
+  <si>
+    <t>90%</t>
   </si>
 </sst>
 </file>
@@ -87,7 +146,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -433,8 +491,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -472,112 +533,354 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K2" s="2"/>
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K3" s="2"/>
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K4" s="2"/>
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K5" s="2"/>
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K6" s="2"/>
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <v>75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K7" s="2"/>
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K8" s="2"/>
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>26.5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K9" s="2"/>
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>200</v>
+      </c>
+      <c r="G9">
+        <v>185</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K10" s="2"/>
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K37" s="2"/>
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="2">
+        <v>46070.812099905103</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/03 Marzo/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DDC35D9-D645-40B6-B7D9-E184D1DA433F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4306C51-4C35-4DE7-8B71-69E85897D3C8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
   <si>
     <t>Año</t>
   </si>
@@ -125,6 +125,60 @@
   </si>
   <si>
     <t>90%</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>113.3%</t>
+  </si>
+  <si>
+    <t>80.7%</t>
+  </si>
+  <si>
+    <t>104.0%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>116.0%</t>
+  </si>
+  <si>
+    <t>68.0%</t>
+  </si>
+  <si>
+    <t>122.0%</t>
+  </si>
+  <si>
+    <t>96.0%</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>112.7%</t>
+  </si>
+  <si>
+    <t>125.0%</t>
+  </si>
+  <si>
+    <t>137.5%</t>
+  </si>
+  <si>
+    <t>94.7%</t>
+  </si>
+  <si>
+    <t>150.0%</t>
+  </si>
+  <si>
+    <t>56.0%</t>
+  </si>
+  <si>
+    <t>158.0%</t>
   </si>
 </sst>
 </file>
@@ -132,7 +186,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -188,7 +242,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,9 +545,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -564,7 +621,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -599,7 +656,7 @@
         <v>17</v>
       </c>
       <c r="K3" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -634,7 +691,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -669,7 +726,7 @@
         <v>17</v>
       </c>
       <c r="K5" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -704,7 +761,7 @@
         <v>17</v>
       </c>
       <c r="K6" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -739,7 +796,7 @@
         <v>17</v>
       </c>
       <c r="K7" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -774,7 +831,7 @@
         <v>17</v>
       </c>
       <c r="K8" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -809,7 +866,7 @@
         <v>17</v>
       </c>
       <c r="K9" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -844,7 +901,7 @@
         <v>17</v>
       </c>
       <c r="K10" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -879,7 +936,707 @@
         <v>17</v>
       </c>
       <c r="K11" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2026</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2026</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>58</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
+      </c>
+      <c r="G18">
+        <v>60.5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2026</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>150</v>
+      </c>
+      <c r="G19">
+        <v>170</v>
+      </c>
+      <c r="H19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2026</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21">
+        <v>100000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2026</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>46</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2026</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23">
+        <v>169</v>
+      </c>
+      <c r="H23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2026</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24">
+        <v>60</v>
+      </c>
+      <c r="G24">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25">
+        <v>100000</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>33</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2026</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>57</v>
+      </c>
+      <c r="H29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2026</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>25</v>
+      </c>
+      <c r="G30">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="2">
+        <v>46135.554853843933</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="2">
+        <v>46135.554853843933</v>
       </c>
     </row>
   </sheetData>
